--- a/output_tcc_var/tabelas/00_resumo_lags_e_estabilidade.xlsx
+++ b/output_tcc_var/tabelas/00_resumo_lags_e_estabilidade.xlsx
@@ -460,19 +460,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D2" t="n">
-        <v>-31.7597473843593</v>
+        <v>-31.80743038199088</v>
       </c>
       <c r="E2" t="n">
-        <v>-30.53361842055245</v>
+        <v>-30.14592894324705</v>
       </c>
       <c r="F2" t="n">
-        <v>-31.2673873963634</v>
+        <v>-31.14009214810709</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
@@ -491,13 +491,13 @@
         <v>271</v>
       </c>
       <c r="D3" t="n">
-        <v>-31.48624395686831</v>
+        <v>-31.48634878017981</v>
       </c>
       <c r="E3" t="n">
-        <v>-30.47605565285777</v>
+        <v>-30.47616047616927</v>
       </c>
       <c r="F3" t="n">
-        <v>-31.08064239660296</v>
+        <v>-31.08074721991445</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
@@ -516,13 +516,13 @@
         <v>271</v>
       </c>
       <c r="D4" t="n">
-        <v>-30.00160038706311</v>
+        <v>-30.00168387366201</v>
       </c>
       <c r="E4" t="n">
-        <v>-28.99141208305257</v>
+        <v>-28.99149556965147</v>
       </c>
       <c r="F4" t="n">
-        <v>-29.59599882679775</v>
+        <v>-29.59608231339665</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
@@ -541,13 +541,13 @@
         <v>271</v>
       </c>
       <c r="D5" t="n">
-        <v>-31.49474604350024</v>
+        <v>-31.49481487549261</v>
       </c>
       <c r="E5" t="n">
-        <v>-30.48455773948969</v>
+        <v>-30.48462657148207</v>
       </c>
       <c r="F5" t="n">
-        <v>-31.08914448323488</v>
+        <v>-31.08921331522725</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -566,13 +566,13 @@
         <v>270</v>
       </c>
       <c r="D6" t="n">
-        <v>-29.80362703259911</v>
+        <v>-29.771889639089</v>
       </c>
       <c r="E6" t="n">
-        <v>-28.57749806879226</v>
+        <v>-28.54576067528215</v>
       </c>
       <c r="F6" t="n">
-        <v>-29.31126704460321</v>
+        <v>-29.2795296510931</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -594,7 +594,7 @@
         <v>-30.26506979329455</v>
       </c>
       <c r="E7" t="n">
-        <v>-29.0389408294877</v>
+        <v>-29.03894082948769</v>
       </c>
       <c r="F7" t="n">
         <v>-29.77270980529865</v>
@@ -616,13 +616,13 @@
         <v>271</v>
       </c>
       <c r="D8" t="n">
-        <v>-28.25466483957304</v>
+        <v>-28.25466483957301</v>
       </c>
       <c r="E8" t="n">
-        <v>-27.2444765355625</v>
+        <v>-27.24447653556247</v>
       </c>
       <c r="F8" t="n">
-        <v>-27.84906327930768</v>
+        <v>-27.84906327930765</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -641,13 +641,13 @@
         <v>271</v>
       </c>
       <c r="D9" t="n">
-        <v>-29.50601870844077</v>
+        <v>-29.50601870844075</v>
       </c>
       <c r="E9" t="n">
-        <v>-28.49583040443023</v>
+        <v>-28.49583040443021</v>
       </c>
       <c r="F9" t="n">
-        <v>-29.10041714817541</v>
+        <v>-29.1004171481754</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
